--- a/光伏配储项目/电价数据/2026/桂竹站.xlsx
+++ b/光伏配储项目/电价数据/2026/桂竹站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.6042000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6800700000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60784</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.59256</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5936699999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46951</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42017</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51746</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19925</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21488</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17577</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20078</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25264</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06217</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15969</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24106</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23033</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.9055700000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22323</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52039</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5360499999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.52618</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60581</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6065199999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72622</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21466</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.78765</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65459</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9340700000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5393600000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27553</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39174</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14347</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24491</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.35012</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.51399</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75387</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.80562</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31339</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12085</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86575</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79361</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75358</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70047</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74572</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86283</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9036900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49708</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46232</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7006599999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55672</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6598099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58188</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85689</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07289</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58351</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93611</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89027</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.55998</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84146</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2501</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05738</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50269</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5869800000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86029</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60529</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.77122</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.84014</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.21253</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15853</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8784400000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26264</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16686</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32566</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10703</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15156</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.71036</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04254</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8939600000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.0531</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.0742</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87876</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81423</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83449</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44097</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48275</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15964</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5462400000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49331</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48788</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.58382</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6655800000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63163</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89673</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58805</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.70135</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77816</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86588</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5233099999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7779400000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72214</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64481</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63693</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.58608</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51139</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57752</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61148</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6013200000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2352</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.73746</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47026</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51078</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5776399999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71856</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71794</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8606900000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59734</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.55048</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60161</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72964</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56275</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8730800000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.69828</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57852</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5147200000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64661</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5138400000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44302</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6398400000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.0167</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5925499999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.65246</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48288</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5338999999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.66062</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51695</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7141000000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.52213</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.48105</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30976</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24453</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26576</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.23889</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23521</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18887</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22364</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08581</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18089</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14614</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45508</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33006</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24522</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21171</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09465999999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22172</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27416</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20888</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19445</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06303</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06124</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32325</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30136</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78496</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8711100000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.7086699999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.59223</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5599700000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65151</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86964</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83411</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48973</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50329</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57737</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23108</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9045700000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24282</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24848</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40418</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26061</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38459</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08565</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65387</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.74283</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.60709</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22849</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05904</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25507</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.66726</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27332</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27916</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22305</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24133</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21338</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20509</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20558</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09264</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22445</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09362999999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26319</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22056</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15738</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20251</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22198</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23828</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24184</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24907</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22195</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24172</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24166</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24899</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22017</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23705</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24057</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22633</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24052</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30685</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44902</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32607</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22251</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5532899999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.53298</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50159</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5710499999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.44591</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6659299999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.84005</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.57813</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.5431900000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.50926</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.49547</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67243</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5370199999999999</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69648</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.51419</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7492300000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.46234</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49057</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22407</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.15189</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24831</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25377</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21861</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24273</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24802</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23588</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22466</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29286</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23087</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33088</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.12495</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63981</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.84362</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31468</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.48542</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.49252</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.44472</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.48989</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6326499999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.56912</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69835</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65588</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7307400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84909</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.68911</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5418200000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45758</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33143</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50426</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.54112</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.61336</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6202000000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68753</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45616</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.60045</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.52089</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.49835</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44811</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.53042</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75464</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60675</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65376</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43833</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37384</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.53542</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.14573</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4655899999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46711</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24119</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27084</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23353</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26408</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23909</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23563</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13962</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13034</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.12937</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.12364</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23459</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.12317</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22192</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22834</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11923</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23548</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11872</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10302</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24979</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23277</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21206</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11403</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18827</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25029</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28592</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26809</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25465</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23051</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27086</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23273</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10735</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25694</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13563</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10099</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10955</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10954</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10777</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10778</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10883</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23749</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09898</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10777</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10794</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22634</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10106</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10097</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11225</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07224999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11541</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00224</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14188</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01597</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00085</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03843</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02207</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19988</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11068</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29959</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.52863</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.21023</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23904</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23093</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21639</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11867</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08086</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09795999999999999</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10823</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.12244</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08764</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14046</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.15278</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27226</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10784</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86772</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8588899999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10723</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09951</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16258</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.12743</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.08965</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66073</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59819</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.07666</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9733099999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.56694</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72484</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6134500000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83016</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82838</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83265</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93036</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.55588</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.60948</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33424</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25338</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43866</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48213</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23416</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11496</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24608</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5701900000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.4942</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32332</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40316</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.48507</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7114199999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47953</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44599</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.73952</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8511599999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.14095</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48855</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5681499999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57541</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.04968</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.88736</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.54075</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64889</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34117</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.26748</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.03768</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6544099999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8845700000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6516900000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5839299999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8082</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74582</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98837</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89078</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.8025599999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7279800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34562</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.14677</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.79275</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.48384</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.57726</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.7971200000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.49141</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5345700000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67296</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.52327</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6597999999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35156</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9159299999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5289700000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49485</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.48068</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50825</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.58933</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.48659</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.46279</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3521</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14314</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12087</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19216</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26065</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15194</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19598</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14081</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.50161</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.55027</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37927</v>
       </c>
     </row>
   </sheetData>
